--- a/valida_reducoes.xlsx
+++ b/valida_reducoes.xlsx
@@ -250,97 +250,97 @@
     <t>H26830001</t>
   </si>
   <si>
-    <t>313 → 311</t>
-  </si>
-  <si>
-    <t>03-32</t>
+    <t>121 → 311</t>
+  </si>
+  <si>
+    <t>Sem linha</t>
   </si>
   <si>
     <t>5116</t>
   </si>
   <si>
-    <t>107 → 306</t>
+    <t>108 → 340 → 311</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>Sem linha</t>
-  </si>
-  <si>
-    <t>115 → 306</t>
+    <t>ALT 11 → 306</t>
   </si>
   <si>
     <t>21 → 18</t>
   </si>
   <si>
-    <t>ALT 25 → 306</t>
-  </si>
-  <si>
-    <t>5114</t>
+    <t>5114 → 311</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>307A → 5116</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>314 → 306</t>
-  </si>
-  <si>
-    <t>124 → 5114 → 5116</t>
-  </si>
-  <si>
-    <t>5114 → 5116</t>
-  </si>
-  <si>
     <t>331 → 311</t>
   </si>
   <si>
-    <t>115 → 5118 → 03-32</t>
-  </si>
-  <si>
-    <t>21 → 03-31</t>
-  </si>
-  <si>
-    <t>5116 → 311</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>320 → 306</t>
-  </si>
-  <si>
-    <t>128 → 5114 → 5116</t>
-  </si>
-  <si>
-    <t>5118 → 03-32</t>
-  </si>
-  <si>
-    <t>03-32 → 311</t>
-  </si>
-  <si>
-    <t>5116 → 18</t>
-  </si>
-  <si>
-    <t>107 → 5118 → 03-32</t>
-  </si>
-  <si>
-    <t>115 → 5114 → 5114 → 18</t>
+    <t>314 → 5116</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>320 → 311</t>
+  </si>
+  <si>
+    <t>105 → 304 → 5116</t>
+  </si>
+  <si>
+    <t>331 → 309 → 5116</t>
+  </si>
+  <si>
+    <t>ALT 11 → 5116</t>
+  </si>
+  <si>
+    <t>340 → 311</t>
+  </si>
+  <si>
+    <t>303 (estimada) → 311</t>
+  </si>
+  <si>
+    <t>23 → 18</t>
+  </si>
+  <si>
+    <t>309 → 5116</t>
+  </si>
+  <si>
+    <t>209 → 5114 → 03 → 18</t>
+  </si>
+  <si>
+    <t>5116 → 03 → 18</t>
+  </si>
+  <si>
+    <t>107 → 5114 → 03 → 18</t>
+  </si>
+  <si>
+    <t>313 → 5114 → 23 → 18</t>
+  </si>
+  <si>
+    <t>03-31 → 5116</t>
+  </si>
+  <si>
+    <t>5114 → 23 → 18</t>
+  </si>
+  <si>
+    <t>115 → 5114 → 22</t>
   </si>
   <si>
     <t>21 → 06</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>341A → 5118 → 03-32</t>
+    <t>5114 → 03 → 18</t>
+  </si>
+  <si>
+    <t>303 (estimada) → 5114 → 23 → 18</t>
+  </si>
+  <si>
+    <t>341A → 5114 → 22</t>
   </si>
 </sst>
 </file>
@@ -771,7 +771,7 @@
         <v>72</v>
       </c>
       <c r="E2">
-        <v>25.874</v>
+        <v>25.153</v>
       </c>
       <c r="F2" t="s">
         <v>74</v>
@@ -783,34 +783,34 @@
         <v>78</v>
       </c>
       <c r="I2">
-        <v>15.246</v>
+        <v>15.293</v>
       </c>
       <c r="J2">
-        <v>41.08</v>
+        <v>39.2</v>
       </c>
       <c r="K2" t="s">
         <v>77</v>
       </c>
       <c r="L2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M2">
-        <v>19.092</v>
+        <v>22.394</v>
       </c>
       <c r="N2">
-        <v>26.21</v>
+        <v>10.97</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q2">
-        <v>19.043</v>
+        <v>25.153</v>
       </c>
       <c r="R2">
-        <v>26.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -827,7 +827,7 @@
         <v>72</v>
       </c>
       <c r="E3">
-        <v>10.861</v>
+        <v>7.468</v>
       </c>
       <c r="F3" t="s">
         <v>74</v>
@@ -839,34 +839,34 @@
         <v>79</v>
       </c>
       <c r="I3">
-        <v>3.553</v>
+        <v>2.191</v>
       </c>
       <c r="J3">
-        <v>67.29000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="K3" t="s">
         <v>77</v>
       </c>
       <c r="L3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M3">
-        <v>8.228</v>
+        <v>5.401</v>
       </c>
       <c r="N3">
-        <v>24.24</v>
+        <v>27.68</v>
       </c>
       <c r="O3" t="s">
         <v>75</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="Q3">
-        <v>8.289</v>
+        <v>9.677</v>
       </c>
       <c r="R3">
-        <v>23.68</v>
+        <v>-29.58</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -883,7 +883,7 @@
         <v>72</v>
       </c>
       <c r="E4">
-        <v>20.484</v>
+        <v>22.645</v>
       </c>
       <c r="F4" t="s">
         <v>74</v>
@@ -895,31 +895,31 @@
         <v>80</v>
       </c>
       <c r="I4">
-        <v>10.689</v>
+        <v>11.121</v>
       </c>
       <c r="J4">
-        <v>47.82</v>
+        <v>50.89</v>
       </c>
       <c r="K4" t="s">
         <v>75</v>
       </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M4">
-        <v>9.298</v>
+        <v>12.135</v>
       </c>
       <c r="N4">
-        <v>54.61</v>
+        <v>46.41</v>
       </c>
       <c r="O4" t="s">
         <v>74</v>
       </c>
       <c r="P4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="Q4">
-        <v>20.484</v>
+        <v>22.645</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>13.89</v>
+        <v>16.253</v>
       </c>
       <c r="F5" t="s">
         <v>75</v>
@@ -951,7 +951,7 @@
         <v>81</v>
       </c>
       <c r="I5">
-        <v>13.89</v>
+        <v>16.253</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -960,25 +960,25 @@
         <v>77</v>
       </c>
       <c r="L5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M5">
-        <v>24.803</v>
+        <v>20.306</v>
       </c>
       <c r="N5">
-        <v>-78.56999999999999</v>
+        <v>-24.94</v>
       </c>
       <c r="O5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>20.923</v>
+        <v>27.171</v>
       </c>
       <c r="R5">
-        <v>-50.63</v>
+        <v>-67.18000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1016,25 +1016,25 @@
         <v>77</v>
       </c>
       <c r="L6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M6">
-        <v>17.894</v>
+        <v>15.569</v>
       </c>
       <c r="N6">
-        <v>-93.45</v>
+        <v>-68.31</v>
       </c>
       <c r="O6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P6" t="s">
         <v>101</v>
       </c>
       <c r="Q6">
-        <v>14.008</v>
+        <v>20.676</v>
       </c>
       <c r="R6">
-        <v>-51.44</v>
+        <v>-123.52</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1051,7 +1051,7 @@
         <v>72</v>
       </c>
       <c r="E7">
-        <v>9.175000000000001</v>
+        <v>3.04</v>
       </c>
       <c r="F7" t="s">
         <v>74</v>
@@ -1060,37 +1060,37 @@
         <v>76</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I7">
         <v>1.542</v>
       </c>
       <c r="J7">
-        <v>83.19</v>
+        <v>49.28</v>
       </c>
       <c r="K7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7">
+        <v>3.04</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
         <v>77</v>
-      </c>
-      <c r="L7" t="s">
-        <v>83</v>
-      </c>
-      <c r="M7">
-        <v>3.592</v>
-      </c>
-      <c r="N7">
-        <v>60.85</v>
-      </c>
-      <c r="O7" t="s">
-        <v>75</v>
       </c>
       <c r="P7" t="s">
         <v>102</v>
       </c>
       <c r="Q7">
-        <v>6.603</v>
+        <v>5.555</v>
       </c>
       <c r="R7">
-        <v>28.03</v>
+        <v>-82.73</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1107,7 +1107,7 @@
         <v>72</v>
       </c>
       <c r="E8">
-        <v>21.857</v>
+        <v>21.275</v>
       </c>
       <c r="F8" t="s">
         <v>74</v>
@@ -1119,34 +1119,34 @@
         <v>80</v>
       </c>
       <c r="I8">
-        <v>13.992</v>
+        <v>14.424</v>
       </c>
       <c r="J8">
-        <v>35.98</v>
+        <v>32.2</v>
       </c>
       <c r="K8" t="s">
         <v>75</v>
       </c>
       <c r="L8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M8">
         <v>16.212</v>
       </c>
       <c r="N8">
-        <v>25.83</v>
+        <v>23.8</v>
       </c>
       <c r="O8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q8">
-        <v>15.027</v>
+        <v>21.275</v>
       </c>
       <c r="R8">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1163,7 +1163,7 @@
         <v>73</v>
       </c>
       <c r="E9">
-        <v>16.14</v>
+        <v>17.575</v>
       </c>
       <c r="F9" t="s">
         <v>75</v>
@@ -1172,37 +1172,37 @@
         <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I9">
-        <v>16.14</v>
+        <v>17.575</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M9">
-        <v>23.172</v>
+        <v>26.368</v>
       </c>
       <c r="N9">
-        <v>-43.57</v>
+        <v>-50.03</v>
       </c>
       <c r="O9" t="s">
         <v>74</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q9">
-        <v>30.002</v>
+        <v>26.264</v>
       </c>
       <c r="R9">
-        <v>-85.89</v>
+        <v>-49.44</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1219,7 +1219,7 @@
         <v>73</v>
       </c>
       <c r="E10">
-        <v>16.319</v>
+        <v>17.772</v>
       </c>
       <c r="F10" t="s">
         <v>75</v>
@@ -1228,37 +1228,37 @@
         <v>74</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I10">
-        <v>14.417</v>
+        <v>14.426</v>
       </c>
       <c r="J10">
-        <v>11.66</v>
+        <v>18.83</v>
       </c>
       <c r="K10" t="s">
         <v>76</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M10">
-        <v>13.39</v>
+        <v>13.601</v>
       </c>
       <c r="N10">
-        <v>17.95</v>
+        <v>23.47</v>
       </c>
       <c r="O10" t="s">
         <v>77</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q10">
-        <v>11.066</v>
+        <v>9.948</v>
       </c>
       <c r="R10">
-        <v>32.19</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1275,46 +1275,46 @@
         <v>72</v>
       </c>
       <c r="E11">
-        <v>26.587</v>
+        <v>26.005</v>
       </c>
       <c r="F11" t="s">
         <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I11">
-        <v>11.407</v>
+        <v>22.954</v>
       </c>
       <c r="J11">
-        <v>57.1</v>
+        <v>11.73</v>
       </c>
       <c r="K11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M11">
-        <v>23.642</v>
+        <v>16.312</v>
       </c>
       <c r="N11">
-        <v>11.08</v>
+        <v>37.27</v>
       </c>
       <c r="O11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="Q11">
-        <v>19.757</v>
+        <v>26.005</v>
       </c>
       <c r="R11">
-        <v>25.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1331,7 +1331,7 @@
         <v>72</v>
       </c>
       <c r="E12">
-        <v>22.296</v>
+        <v>21.918</v>
       </c>
       <c r="F12" t="s">
         <v>74</v>
@@ -1343,34 +1343,34 @@
         <v>80</v>
       </c>
       <c r="I12">
-        <v>13.778</v>
+        <v>14.21</v>
       </c>
       <c r="J12">
-        <v>38.2</v>
+        <v>35.17</v>
       </c>
       <c r="K12" t="s">
         <v>75</v>
       </c>
       <c r="L12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M12">
         <v>16.741</v>
       </c>
       <c r="N12">
-        <v>24.91</v>
+        <v>23.62</v>
       </c>
       <c r="O12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="Q12">
-        <v>15.466</v>
+        <v>21.918</v>
       </c>
       <c r="R12">
-        <v>30.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1387,7 +1387,7 @@
         <v>73</v>
       </c>
       <c r="E13">
-        <v>17.983</v>
+        <v>15.986</v>
       </c>
       <c r="F13" t="s">
         <v>75</v>
@@ -1402,31 +1402,31 @@
         <v>22.7</v>
       </c>
       <c r="J13">
-        <v>-26.23</v>
+        <v>-42</v>
       </c>
       <c r="K13" t="s">
         <v>75</v>
       </c>
       <c r="L13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M13">
-        <v>17.983</v>
+        <v>15.986</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q13">
-        <v>19.503</v>
+        <v>25.751</v>
       </c>
       <c r="R13">
-        <v>-8.449999999999999</v>
+        <v>-61.08</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1443,7 +1443,7 @@
         <v>73</v>
       </c>
       <c r="E14">
-        <v>4.595</v>
+        <v>5.117</v>
       </c>
       <c r="F14" t="s">
         <v>75</v>
@@ -1452,10 +1452,10 @@
         <v>75</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I14">
-        <v>4.595</v>
+        <v>5.117</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1464,25 +1464,25 @@
         <v>74</v>
       </c>
       <c r="L14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M14">
-        <v>5.829</v>
+        <v>13.358</v>
       </c>
       <c r="N14">
-        <v>-26.86</v>
+        <v>-161.05</v>
       </c>
       <c r="O14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P14" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="Q14">
-        <v>5.575</v>
+        <v>12.532</v>
       </c>
       <c r="R14">
-        <v>-21.33</v>
+        <v>-144.91</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1499,7 +1499,7 @@
         <v>72</v>
       </c>
       <c r="E15">
-        <v>9.301</v>
+        <v>2.915</v>
       </c>
       <c r="F15" t="s">
         <v>74</v>
@@ -1508,37 +1508,37 @@
         <v>76</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I15">
         <v>1.417</v>
       </c>
       <c r="J15">
-        <v>84.77</v>
+        <v>51.39</v>
       </c>
       <c r="K15" t="s">
+        <v>74</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15">
+        <v>2.915</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
         <v>77</v>
-      </c>
-      <c r="L15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M15">
-        <v>3.717</v>
-      </c>
-      <c r="N15">
-        <v>60.04</v>
-      </c>
-      <c r="O15" t="s">
-        <v>75</v>
       </c>
       <c r="P15" t="s">
         <v>102</v>
       </c>
       <c r="Q15">
-        <v>6.729</v>
+        <v>10.373</v>
       </c>
       <c r="R15">
-        <v>27.65</v>
+        <v>-255.85</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1564,7 +1564,7 @@
         <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I16">
         <v>5.457</v>
@@ -1576,7 +1576,7 @@
         <v>76</v>
       </c>
       <c r="L16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M16">
         <v>4.633</v>
@@ -1588,13 +1588,13 @@
         <v>77</v>
       </c>
       <c r="P16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q16">
-        <v>9.465</v>
+        <v>5.739</v>
       </c>
       <c r="R16">
-        <v>-73.45</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1611,7 +1611,7 @@
         <v>73</v>
       </c>
       <c r="E17">
-        <v>11.365</v>
+        <v>11.928</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
@@ -1620,37 +1620,37 @@
         <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I17">
         <v>5.606</v>
       </c>
       <c r="J17">
-        <v>50.67</v>
+        <v>53</v>
       </c>
       <c r="K17" t="s">
         <v>76</v>
       </c>
       <c r="L17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M17">
         <v>4.782</v>
       </c>
       <c r="N17">
-        <v>57.92</v>
+        <v>59.91</v>
       </c>
       <c r="O17" t="s">
         <v>77</v>
       </c>
       <c r="P17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q17">
-        <v>8.618</v>
+        <v>5.77</v>
       </c>
       <c r="R17">
-        <v>24.17</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1667,7 +1667,7 @@
         <v>73</v>
       </c>
       <c r="E18">
-        <v>10.882</v>
+        <v>11.917</v>
       </c>
       <c r="F18" t="s">
         <v>75</v>
@@ -1679,19 +1679,19 @@
         <v>80</v>
       </c>
       <c r="I18">
-        <v>10.978</v>
+        <v>11.408</v>
       </c>
       <c r="J18">
-        <v>-0.88</v>
+        <v>4.27</v>
       </c>
       <c r="K18" t="s">
         <v>75</v>
       </c>
       <c r="L18" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="M18">
-        <v>10.882</v>
+        <v>11.917</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -1700,13 +1700,13 @@
         <v>74</v>
       </c>
       <c r="P18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="Q18">
-        <v>20.771</v>
+        <v>22.934</v>
       </c>
       <c r="R18">
-        <v>-90.87</v>
+        <v>-92.45</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1723,7 +1723,7 @@
         <v>73</v>
       </c>
       <c r="E19">
-        <v>10.877</v>
+        <v>12.646</v>
       </c>
       <c r="F19" t="s">
         <v>75</v>
@@ -1732,37 +1732,37 @@
         <v>74</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I19">
         <v>6.421</v>
       </c>
       <c r="J19">
-        <v>40.97</v>
+        <v>49.23</v>
       </c>
       <c r="K19" t="s">
         <v>76</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M19">
         <v>5.597</v>
       </c>
       <c r="N19">
-        <v>48.54</v>
+        <v>55.74</v>
       </c>
       <c r="O19" t="s">
         <v>77</v>
       </c>
       <c r="P19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q19">
-        <v>8.875999999999999</v>
+        <v>6.049</v>
       </c>
       <c r="R19">
-        <v>18.4</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1809,16 +1809,16 @@
         <v>-28.15</v>
       </c>
       <c r="O20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q20">
-        <v>18.584</v>
+        <v>24.832</v>
       </c>
       <c r="R20">
-        <v>-9.34</v>
+        <v>-46.1</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1835,7 +1835,7 @@
         <v>73</v>
       </c>
       <c r="E21">
-        <v>13.474</v>
+        <v>11.053</v>
       </c>
       <c r="F21" t="s">
         <v>75</v>
@@ -1844,10 +1844,10 @@
         <v>75</v>
       </c>
       <c r="H21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I21">
-        <v>13.474</v>
+        <v>11.053</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1856,25 +1856,25 @@
         <v>77</v>
       </c>
       <c r="L21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M21">
-        <v>24.028</v>
+        <v>15.066</v>
       </c>
       <c r="N21">
-        <v>-78.33</v>
+        <v>-36.31</v>
       </c>
       <c r="O21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P21" t="s">
         <v>108</v>
       </c>
       <c r="Q21">
-        <v>17.749</v>
+        <v>20.842</v>
       </c>
       <c r="R21">
-        <v>-31.73</v>
+        <v>-88.56</v>
       </c>
     </row>
   </sheetData>

--- a/valida_reducoes.xlsx
+++ b/valida_reducoes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="113">
   <si>
     <t>MT</t>
   </si>
@@ -124,6 +124,9 @@
     <t>31898</t>
   </si>
   <si>
+    <t>32896</t>
+  </si>
+  <si>
     <t>6030</t>
   </si>
   <si>
@@ -226,6 +229,9 @@
     <t>R. Pedro Bassi 505, Centro, Jacareí, SP, 12327480, Brasil</t>
   </si>
   <si>
+    <t>Rua Jose Jorge Abrahao 495, Jardim Dora, Jacareí, SP, 12301331, Brasil</t>
+  </si>
+  <si>
     <t>R. Vilaça 456, Centro, São José dos Campos, SP, 12210000, Brasil</t>
   </si>
   <si>
@@ -247,100 +253,106 @@
     <t>H27990002</t>
   </si>
   <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Sem linha</t>
+  </si>
+  <si>
+    <t>314 → 306</t>
+  </si>
+  <si>
+    <t>108 → 306</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>5114 → 306</t>
+  </si>
+  <si>
+    <t>115 → 311</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>201 → 306</t>
+  </si>
+  <si>
+    <t>315 → 306</t>
+  </si>
+  <si>
+    <t>5114</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>320 → 311</t>
+  </si>
+  <si>
     <t>H26830001</t>
   </si>
   <si>
-    <t>121 → 311</t>
-  </si>
-  <si>
-    <t>Sem linha</t>
+    <t>214 → 5114 → 22</t>
+  </si>
+  <si>
+    <t>5116 → 22</t>
+  </si>
+  <si>
+    <t>124 → 5114 → 22</t>
+  </si>
+  <si>
+    <t>5114 → 22</t>
   </si>
   <si>
     <t>5116</t>
   </si>
   <si>
-    <t>108 → 340 → 311</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>ALT 11 → 306</t>
-  </si>
-  <si>
-    <t>21 → 18</t>
-  </si>
-  <si>
-    <t>5114 → 311</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>331 → 311</t>
-  </si>
-  <si>
-    <t>314 → 5116</t>
+    <t>122 → 5116</t>
+  </si>
+  <si>
+    <t>21 → 22</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>128 → 5114 → 22</t>
+  </si>
+  <si>
+    <t>305 → 5114 → 03 → 03-31</t>
+  </si>
+  <si>
+    <t>327 → 5114 → 03 → 03-31</t>
+  </si>
+  <si>
+    <t>107 → 5114 → 03 → 03-31</t>
+  </si>
+  <si>
+    <t>5114 → 03 → 03-31</t>
+  </si>
+  <si>
+    <t>115 → 5114 → 22</t>
+  </si>
+  <si>
+    <t>21 → 06</t>
+  </si>
+  <si>
+    <t>307B → 5114 → 03 → 03-31</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>320 → 311</t>
-  </si>
-  <si>
-    <t>105 → 304 → 5116</t>
-  </si>
-  <si>
-    <t>331 → 309 → 5116</t>
-  </si>
-  <si>
-    <t>ALT 11 → 5116</t>
-  </si>
-  <si>
-    <t>340 → 311</t>
-  </si>
-  <si>
-    <t>303 (estimada) → 311</t>
-  </si>
-  <si>
-    <t>23 → 18</t>
-  </si>
-  <si>
-    <t>309 → 5116</t>
-  </si>
-  <si>
-    <t>209 → 5114 → 03 → 18</t>
-  </si>
-  <si>
-    <t>5116 → 03 → 18</t>
-  </si>
-  <si>
-    <t>107 → 5114 → 03 → 18</t>
-  </si>
-  <si>
-    <t>313 → 5114 → 23 → 18</t>
-  </si>
-  <si>
-    <t>03-31 → 5116</t>
-  </si>
-  <si>
-    <t>5114 → 23 → 18</t>
-  </si>
-  <si>
-    <t>115 → 5114 → 22</t>
-  </si>
-  <si>
-    <t>21 → 06</t>
-  </si>
-  <si>
-    <t>5114 → 03 → 18</t>
-  </si>
-  <si>
-    <t>303 (estimada) → 5114 → 23 → 18</t>
-  </si>
-  <si>
-    <t>341A → 5114 → 22</t>
+    <t>06</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>128 → 5114 → 03 → 03-31</t>
   </si>
 </sst>
 </file>
@@ -698,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -762,55 +774,55 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2">
-        <v>25.153</v>
+        <v>20.351</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2">
+        <v>13.447</v>
+      </c>
+      <c r="J2">
+        <v>33.92</v>
+      </c>
+      <c r="K2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2">
+        <v>20.351</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
         <v>78</v>
       </c>
-      <c r="I2">
-        <v>15.293</v>
-      </c>
-      <c r="J2">
-        <v>39.2</v>
-      </c>
-      <c r="K2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M2">
-        <v>22.394</v>
-      </c>
-      <c r="N2">
-        <v>10.97</v>
-      </c>
-      <c r="O2" t="s">
-        <v>74</v>
-      </c>
       <c r="P2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q2">
-        <v>25.153</v>
+        <v>21.691</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -818,31 +830,31 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>7.468</v>
+        <v>9.68</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>2.191</v>
       </c>
       <c r="J3">
-        <v>70.66</v>
+        <v>77.37</v>
       </c>
       <c r="K3" t="s">
         <v>77</v>
@@ -851,22 +863,22 @@
         <v>89</v>
       </c>
       <c r="M3">
-        <v>5.401</v>
+        <v>9.146000000000001</v>
       </c>
       <c r="N3">
-        <v>27.68</v>
+        <v>5.52</v>
       </c>
       <c r="O3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q3">
-        <v>9.677</v>
+        <v>9.68</v>
       </c>
       <c r="R3">
-        <v>-29.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -874,55 +886,55 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4">
-        <v>22.645</v>
+        <v>19.857</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
         <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4">
-        <v>11.121</v>
+        <v>10.734</v>
       </c>
       <c r="J4">
-        <v>50.89</v>
+        <v>45.94</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M4">
-        <v>12.135</v>
+        <v>19.857</v>
       </c>
       <c r="N4">
-        <v>46.41</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Q4">
-        <v>22.645</v>
+        <v>24.957</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-25.68</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -930,55 +942,55 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>16.253</v>
+        <v>15.321</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5">
-        <v>16.253</v>
+        <v>15.321</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="M5">
-        <v>20.306</v>
+        <v>21.856</v>
       </c>
       <c r="N5">
-        <v>-24.94</v>
+        <v>-42.65</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q5">
-        <v>27.171</v>
+        <v>23.701</v>
       </c>
       <c r="R5">
-        <v>-67.18000000000001</v>
+        <v>-54.7</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -986,25 +998,25 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>9.25</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>9.25</v>
@@ -1013,28 +1025,28 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M6">
-        <v>15.569</v>
+        <v>15.026</v>
       </c>
       <c r="N6">
-        <v>-68.31</v>
+        <v>-62.44</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q6">
-        <v>20.676</v>
+        <v>17.828</v>
       </c>
       <c r="R6">
-        <v>-123.52</v>
+        <v>-92.73999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1042,25 +1054,25 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7">
         <v>3.04</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7">
         <v>1.542</v>
@@ -1069,28 +1081,28 @@
         <v>49.28</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="M7">
+        <v>7.619</v>
+      </c>
+      <c r="N7">
+        <v>-150.62</v>
+      </c>
+      <c r="O7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
         <v>3.04</v>
       </c>
-      <c r="N7">
+      <c r="R7">
         <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>77</v>
-      </c>
-      <c r="P7" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q7">
-        <v>5.555</v>
-      </c>
-      <c r="R7">
-        <v>-82.73</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1098,55 +1110,55 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E8">
-        <v>21.275</v>
+        <v>23.16</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
         <v>77</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I8">
-        <v>14.424</v>
+        <v>12.736</v>
       </c>
       <c r="J8">
-        <v>32.2</v>
+        <v>45.01</v>
       </c>
       <c r="K8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M8">
-        <v>16.212</v>
+        <v>23.16</v>
       </c>
       <c r="N8">
-        <v>23.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q8">
-        <v>21.275</v>
+        <v>18.847</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1154,55 +1166,55 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E9">
-        <v>17.575</v>
+        <v>21.62</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I9">
-        <v>17.575</v>
+        <v>21.62</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M9">
-        <v>26.368</v>
+        <v>27.835</v>
       </c>
       <c r="N9">
-        <v>-50.03</v>
+        <v>-28.75</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q9">
-        <v>26.264</v>
+        <v>24.11</v>
       </c>
       <c r="R9">
-        <v>-49.44</v>
+        <v>-11.52</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1210,49 +1222,49 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>17.772</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I10">
-        <v>14.426</v>
+        <v>11.165</v>
       </c>
       <c r="J10">
-        <v>18.83</v>
+        <v>37.18</v>
       </c>
       <c r="K10" t="s">
         <v>76</v>
       </c>
       <c r="L10" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="M10">
-        <v>13.601</v>
+        <v>15.076</v>
       </c>
       <c r="N10">
-        <v>23.47</v>
+        <v>15.17</v>
       </c>
       <c r="O10" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q10">
         <v>9.948</v>
@@ -1266,55 +1278,55 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11">
-        <v>26.005</v>
+        <v>20.695</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
         <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I11">
-        <v>22.954</v>
+        <v>12.843</v>
       </c>
       <c r="J11">
-        <v>11.73</v>
+        <v>37.94</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M11">
-        <v>16.312</v>
+        <v>20.695</v>
       </c>
       <c r="N11">
-        <v>37.27</v>
+        <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q11">
-        <v>26.005</v>
+        <v>22.54</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1322,55 +1334,55 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12">
-        <v>21.918</v>
+        <v>22.946</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
         <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I12">
-        <v>14.21</v>
+        <v>16.229</v>
       </c>
       <c r="J12">
-        <v>35.17</v>
+        <v>29.27</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L12" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M12">
-        <v>16.741</v>
+        <v>22.946</v>
       </c>
       <c r="N12">
-        <v>23.62</v>
+        <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q12">
-        <v>21.918</v>
+        <v>19.798</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1378,55 +1390,55 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13">
-        <v>15.986</v>
+        <v>12.374</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s">
         <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I13">
-        <v>22.7</v>
+        <v>12.374</v>
       </c>
       <c r="J13">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M13">
-        <v>15.986</v>
+        <v>20.441</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>-65.19</v>
       </c>
       <c r="O13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q13">
-        <v>25.751</v>
+        <v>22.286</v>
       </c>
       <c r="R13">
-        <v>-61.08</v>
+        <v>-80.09999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1434,55 +1446,55 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14">
-        <v>5.117</v>
+        <v>4.61</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I14">
-        <v>5.117</v>
+        <v>4.61</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>13.358</v>
+        <v>5.829</v>
       </c>
       <c r="N14">
-        <v>-161.05</v>
+        <v>-26.44</v>
       </c>
       <c r="O14" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="Q14">
-        <v>12.532</v>
+        <v>4.276</v>
       </c>
       <c r="R14">
-        <v>-144.91</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1490,25 +1502,25 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E15">
         <v>2.915</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15">
         <v>1.417</v>
@@ -1517,28 +1529,28 @@
         <v>51.39</v>
       </c>
       <c r="K15" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="L15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="M15">
+        <v>7.565</v>
+      </c>
+      <c r="N15">
+        <v>-159.52</v>
+      </c>
+      <c r="O15" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q15">
         <v>2.915</v>
       </c>
-      <c r="N15">
+      <c r="R15">
         <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>77</v>
-      </c>
-      <c r="P15" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q15">
-        <v>10.373</v>
-      </c>
-      <c r="R15">
-        <v>-255.85</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1546,25 +1558,25 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16">
         <v>5.457</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I16">
         <v>5.457</v>
@@ -1573,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M16">
         <v>4.633</v>
@@ -1585,16 +1597,16 @@
         <v>15.1</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q16">
-        <v>5.739</v>
+        <v>8.347</v>
       </c>
       <c r="R16">
-        <v>-5.17</v>
+        <v>-52.96</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1602,55 +1614,55 @@
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E17">
-        <v>11.928</v>
+        <v>12.807</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I17">
         <v>5.606</v>
       </c>
       <c r="J17">
-        <v>53</v>
+        <v>56.23</v>
       </c>
       <c r="K17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M17">
         <v>4.782</v>
       </c>
       <c r="N17">
-        <v>59.91</v>
+        <v>62.66</v>
       </c>
       <c r="O17" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="P17" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q17">
-        <v>5.77</v>
+        <v>7.478</v>
       </c>
       <c r="R17">
-        <v>51.63</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1658,55 +1670,55 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E18">
-        <v>11.917</v>
+        <v>11.022</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
         <v>77</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18">
-        <v>11.408</v>
+        <v>11.022</v>
       </c>
       <c r="J18">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M18">
-        <v>11.917</v>
+        <v>20.146</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>-82.78</v>
       </c>
       <c r="O18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P18" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="Q18">
-        <v>22.934</v>
+        <v>22.364</v>
       </c>
       <c r="R18">
-        <v>-92.45</v>
+        <v>-102.9</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1714,55 +1726,55 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E19">
-        <v>12.646</v>
+        <v>12.324</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I19">
         <v>6.421</v>
       </c>
       <c r="J19">
-        <v>49.23</v>
+        <v>47.9</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M19">
         <v>5.597</v>
       </c>
       <c r="N19">
-        <v>55.74</v>
+        <v>54.58</v>
       </c>
       <c r="O19" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q19">
-        <v>6.049</v>
+        <v>7.757</v>
       </c>
       <c r="R19">
-        <v>52.17</v>
+        <v>37.06</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1770,55 +1782,55 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20">
-        <v>16.996</v>
+        <v>6.661</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I20">
-        <v>16.996</v>
+        <v>5.441</v>
       </c>
       <c r="J20">
+        <v>18.32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" t="s">
+        <v>100</v>
+      </c>
+      <c r="M20">
+        <v>6.661</v>
+      </c>
+      <c r="N20">
         <v>0</v>
       </c>
-      <c r="K20" t="s">
-        <v>77</v>
-      </c>
-      <c r="L20" t="s">
-        <v>80</v>
-      </c>
-      <c r="M20">
-        <v>21.781</v>
-      </c>
-      <c r="N20">
-        <v>-28.15</v>
-      </c>
       <c r="O20" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="P20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="Q20">
-        <v>24.832</v>
+        <v>4.339</v>
       </c>
       <c r="R20">
-        <v>-46.1</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1826,55 +1838,111 @@
         <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E21">
-        <v>11.053</v>
+        <v>13.888</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I21">
-        <v>11.053</v>
+        <v>13.888</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M21">
-        <v>15.066</v>
+        <v>19.522</v>
       </c>
       <c r="N21">
-        <v>-36.31</v>
+        <v>-40.57</v>
       </c>
       <c r="O21" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q21">
-        <v>20.842</v>
+        <v>21.367</v>
       </c>
       <c r="R21">
-        <v>-88.56</v>
+        <v>-53.85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22">
+        <v>13.474</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22">
+        <v>13.474</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" t="s">
+        <v>101</v>
+      </c>
+      <c r="M22">
+        <v>18.6</v>
+      </c>
+      <c r="N22">
+        <v>-38.04</v>
+      </c>
+      <c r="O22" t="s">
+        <v>78</v>
+      </c>
+      <c r="P22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q22">
+        <v>20.445</v>
+      </c>
+      <c r="R22">
+        <v>-51.74</v>
       </c>
     </row>
   </sheetData>
